--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{18F178BC-785D-4E68-A6C0-B19E509B048E}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F030A16B-E8EE-44A7-AA38-DD1C6844BF95}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
+    <sheet name="Plan2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>COMPRIMENTO</t>
   </si>
@@ -79,6 +80,18 @@
   </si>
   <si>
     <t>2,79 m</t>
+  </si>
+  <si>
+    <t>Capacidade deposito</t>
+  </si>
+  <si>
+    <t>1000l</t>
+  </si>
+  <si>
+    <t>Moldova e Mare</t>
+  </si>
+  <si>
+    <t>Acolo e vinul Bun</t>
   </si>
 </sst>
 </file>
@@ -399,11 +412,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="169.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="178.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -466,34 +479,64 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB4F00A-C341-4239-83CC-89D23E10C569}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="169.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F030A16B-E8EE-44A7-AA38-DD1C6844BF95}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB37A1E-F2F3-464E-99CE-3143906CC26A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>COMPRIMENTO</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>Acolo e vinul Bun</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>13l</t>
+  </si>
+  <si>
+    <t>manele</t>
   </si>
 </sst>
 </file>
@@ -412,7 +421,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
@@ -483,6 +492,22 @@
       </c>
       <c r="B8" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="1">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
+++ b/Tipologias/Tipos de Reboque/Lona/Lona standard/Especificações Técnicas e Descrição.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tja-my.sharepoint.com/personal/artiom_fedco_tja_pt/Documents/Ambiente de Trabalho/Tipologias/Tipologias/Tipos de Reboque/Lona/Lona standard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB37A1E-F2F3-464E-99CE-3143906CC26A}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_AD4D361C20488DEA4E38A0536C9D488A5ADEDD80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{665D42B2-F5B6-4E38-B54F-A24A0D949B37}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>COMPRIMENTO</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>13l</t>
-  </si>
-  <si>
-    <t>manele</t>
   </si>
 </sst>
 </file>
@@ -421,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55.77734375" bestFit="1" customWidth="1"/>
@@ -500,14 +497,6 @@
       </c>
       <c r="B9" s="1" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="1">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
